--- a/xlsx/可破坏物数据.xlsx
+++ b/xlsx/可破坏物数据.xlsx
@@ -62,7 +62,6 @@
     <col min="2" max="2" width="13.7578125" customWidth="true"/>
     <col min="3" max="3" width="10.81640625" customWidth="true"/>
     <col min="4" max="4" width="70.3125" customWidth="true"/>
-    <col min="5" max="5" width="18.5859375" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -84,11 +83,6 @@
       <c r="D1" t="inlineStr">
         <is>
           <t>模型文件</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>编辑器附加数据</t>
         </is>
       </c>
     </row>
@@ -113,11 +107,6 @@
           <t>file</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>W2LObject</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -140,11 +129,6 @@
           <t>Doodads\Barrens\Rocks\BarrensFissure\BarrensFissure0.mdl</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
